--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484121_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484121_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4794</v>
+        <v>9.041700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5177</v>
+        <v>5.1922</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9618</v>
+        <v>3.8496</v>
       </c>
       <c r="G2" t="n">
         <v>3.5105</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8977</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4989</v>
+        <v>1.1734</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3988</v>
+        <v>1.2865</v>
       </c>
       <c r="V2" t="n">
         <v>1.881</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2746</v>
+        <v>5.0333</v>
       </c>
       <c r="E3" t="n">
-        <v>3.99</v>
+        <v>4.6646</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2846</v>
+        <v>0.3687</v>
       </c>
       <c r="G3" t="n">
         <v>4.1756</v>
@@ -688,13 +688,13 @@
         <v>0.7935</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.6674</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5611</v>
+        <v>0.1134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4698</v>
+        <v>0.554</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6032</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8321</v>
+        <v>3.388</v>
       </c>
       <c r="E4" t="n">
-        <v>1.469</v>
+        <v>1.3897</v>
       </c>
       <c r="F4" t="n">
-        <v>2.363</v>
+        <v>1.9983</v>
       </c>
       <c r="G4" t="n">
         <v>1.3687</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3245</v>
+        <v>1.8804</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1791</v>
+        <v>1.0997</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1454</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.3373</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>P. RIOS CADENAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0806</v>
+        <v>2.4938</v>
       </c>
       <c r="E5" t="n">
-        <v>1.088</v>
+        <v>2.0331</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9926</v>
+        <v>0.4607</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5569</v>
+        <v>1.4608</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0236</v>
+        <v>0.7509</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5805</v>
+        <v>0.7099</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0007</v>
+        <v>3.297</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5991</v>
+        <v>1.4017</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4016</v>
+        <v>1.8953</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5576</v>
+        <v>-1.8362</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5755</v>
+        <v>-0.6509</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9821</v>
+        <v>-1.1853</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9677</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>2.579</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>5.0379</v>
+        <v>1.2314</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4635</v>
+        <v>0.72</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5745</v>
+        <v>0.5115</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0118</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4341</v>
+        <v>0.9287</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0458</v>
+        <v>0.4563</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3883</v>
+        <v>0.4724</v>
       </c>
       <c r="G6" t="n">
         <v>-3.3938</v>
@@ -922,13 +922,13 @@
         <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6295</v>
+        <v>2.1242</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9216</v>
+        <v>1.3321</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7079</v>
+        <v>0.792</v>
       </c>
       <c r="V6" t="n">
         <v>1.2065</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. RIOS CADENAS</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2403</v>
+        <v>0.3947</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2566</v>
+        <v>1.0189</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0162</v>
+        <v>-0.6242</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4608</v>
+        <v>-1.7795</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7509</v>
+        <v>1.0539</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7099</v>
+        <v>-2.8334</v>
       </c>
       <c r="J7" t="n">
-        <v>3.297</v>
+        <v>0.6107</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4017</v>
+        <v>1.8506</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8953</v>
+        <v>-1.2399</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8362</v>
+        <v>-2.3902</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6509</v>
+        <v>-0.7967</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1853</v>
+        <v>-1.5935</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0221</v>
+        <v>1.0515</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0566</v>
+        <v>0.4082</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0345</v>
+        <v>0.6433</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5427</v>
+        <v>0.2962</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2229</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6803</v>
+        <v>0.8804</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7795</v>
+        <v>-0.5569</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0539</v>
+        <v>1.0236</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8334</v>
+        <v>-1.5805</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6107</v>
+        <v>2.0007</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8506</v>
+        <v>1.5991</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2399</v>
+        <v>0.4016</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3902</v>
+        <v>-2.5576</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7967</v>
+        <v>-0.5755</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5935</v>
+        <v>-1.9821</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3887</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3887</v>
+        <v>2.579</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1994</v>
+        <v>3.2536</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6122</v>
+        <v>1.7913</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5872000000000001</v>
+        <v>1.4622</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.266</v>
+        <v>-1.0118</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. NDOUR</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.153</v>
+        <v>0.2043</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0422</v>
+        <v>1.6739</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1952</v>
+        <v>-1.4695</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1815</v>
+        <v>0.6796</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1815</v>
+        <v>0.7458</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0202</v>
+        <v>3.0681</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0202</v>
+        <v>0.7311</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.337</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2016</v>
+        <v>-2.3885</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2016</v>
+        <v>0.0147</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-2.4032</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0623</v>
+        <v>0.136</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0623</v>
+        <v>-0.4024</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.5384</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>S. NDOUR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1539</v>
+        <v>0.153</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2034</v>
+        <v>-0.0422</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3573</v>
+        <v>0.1952</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6796</v>
+        <v>-0.1815</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7458</v>
+        <v>-0.1815</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.0681</v>
+        <v>0.0202</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7311</v>
+        <v>0.0202</v>
       </c>
       <c r="L10" t="n">
-        <v>2.337</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3885</v>
+        <v>-0.2016</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0147</v>
+        <v>-0.2016</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4032</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2222</v>
+        <v>-0.0623</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8728</v>
+        <v>-0.0623</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6506</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2133</v>
+        <v>0.1208</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9294</v>
+        <v>1.2355</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1427</v>
+        <v>-1.1147</v>
       </c>
       <c r="G11" t="n">
         <v>1.1611</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3781</v>
+        <v>-0.0439</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4988</v>
+        <v>-0.1927</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1207</v>
+        <v>0.1488</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7979000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7484</v>
+        <v>-1.5101</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3658</v>
+        <v>-0.0994</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3826</v>
+        <v>-1.4107</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5261</v>
@@ -1390,13 +1390,13 @@
         <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5515</v>
+        <v>-0.3132</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4364</v>
+        <v>-0.17</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1151</v>
+        <v>-0.1432</v>
       </c>
       <c r="V12" t="n">
         <v>-0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.9212</v>
+        <v>20.5444</v>
       </c>
       <c r="E13" t="n">
-        <v>16.3148</v>
+        <v>16.9384</v>
       </c>
       <c r="F13" t="n">
-        <v>3.606400000000001</v>
+        <v>3.6062</v>
       </c>
       <c r="G13" t="n">
         <v>4.9185</v>
@@ -1468,16 +1468,16 @@
         <v>15.8708</v>
       </c>
       <c r="S13" t="n">
-        <v>11.7615</v>
+        <v>12.3851</v>
       </c>
       <c r="T13" t="n">
-        <v>5.1873</v>
+        <v>5.8107</v>
       </c>
       <c r="U13" t="n">
-        <v>6.5743</v>
+        <v>6.574199999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7266000000000001</v>
+        <v>-0.7266000000000004</v>
       </c>
       <c r="W13" t="n">
         <v>2.0045</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5012</v>
+        <v>5.8174</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0092</v>
+        <v>6.2132</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.508</v>
+        <v>-0.3958</v>
       </c>
       <c r="G14" t="n">
         <v>4.096</v>
@@ -1546,13 +1546,13 @@
         <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7301</v>
+        <v>-0.4138</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7368</v>
+        <v>-0.5327</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0067</v>
+        <v>0.1189</v>
       </c>
       <c r="V14" t="n">
         <v>1.7384</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3253</v>
+        <v>2.7436</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2074</v>
+        <v>3.5135</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8822</v>
+        <v>-0.7699</v>
       </c>
       <c r="G15" t="n">
         <v>3.1347</v>
@@ -1624,13 +1624,13 @@
         <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7301</v>
+        <v>-0.3118</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4988</v>
+        <v>-0.1927</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2313</v>
+        <v>-0.1191</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6745</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5152</v>
+        <v>-0.3852</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2182</v>
+        <v>0.3202</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7335</v>
+        <v>-0.7054</v>
       </c>
       <c r="G16" t="n">
         <v>0.5317</v>
@@ -1702,13 +1702,13 @@
         <v>0.1984</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.055</v>
+        <v>0.0751</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2494</v>
+        <v>-0.1474</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1944</v>
+        <v>0.2224</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7232</v>
+        <v>-0.475</v>
       </c>
       <c r="E17" t="n">
         <v>2.3329</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0562</v>
+        <v>-2.8079</v>
       </c>
       <c r="G17" t="n">
         <v>0.4599</v>
@@ -1780,13 +1780,13 @@
         <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.7026</v>
+        <v>-2.4543</v>
       </c>
       <c r="T17" t="n">
         <v>-1.3602</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3423</v>
+        <v>-1.0941</v>
       </c>
       <c r="V17" t="n">
         <v>-0.266</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7897</v>
+        <v>-0.8203</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7913</v>
+        <v>-0.4852</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0016</v>
+        <v>-0.3351</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4863</v>
@@ -1858,13 +1858,13 @@
         <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2403</v>
+        <v>0.2097</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6744</v>
+        <v>-0.3684</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9147</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3373</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7507</v>
+        <v>-1.5662</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8496</v>
+        <v>0.6456</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6003</v>
+        <v>-2.2118</v>
       </c>
       <c r="G19" t="n">
         <v>0.9202</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.1272</v>
+        <v>-1.9428</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.493</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6342</v>
+        <v>-1.2457</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9405</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7692</v>
+        <v>-2.0805</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4152</v>
+        <v>0.8233</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1844</v>
+        <v>-2.9039</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0461</v>
@@ -2014,13 +2014,13 @@
         <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5247</v>
+        <v>-0.8361</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0599</v>
+        <v>-0.6518</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4649</v>
+        <v>-0.1843</v>
       </c>
       <c r="V20" t="n">
         <v>0.6032</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2263</v>
+        <v>-6.159</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0905</v>
+        <v>-3.9067</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1359</v>
+        <v>-2.2523</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4482</v>
@@ -2092,13 +2092,13 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5878</v>
+        <v>-1.5205</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2382</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.826</v>
+        <v>-0.9424</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9259</v>
+        <v>-7.0296</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1079</v>
+        <v>-5.516</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.818</v>
+        <v>-1.5136</v>
       </c>
       <c r="G22" t="n">
         <v>-1.421</v>
@@ -2170,13 +2170,13 @@
         <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3307</v>
+        <v>-2.4345</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.68</v>
+        <v>-1.0882</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6507</v>
+        <v>-1.3463</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.0471</v>
+        <v>-9.286</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.6491</v>
+        <v>-7.547</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.398</v>
+        <v>-1.7389</v>
       </c>
       <c r="G23" t="n">
         <v>-5.6593</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2136</v>
+        <v>-1.4525</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0599</v>
+        <v>-0.9578</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1538</v>
+        <v>-0.4947</v>
       </c>
       <c r="V23" t="n">
         <v>0.6032</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.9208</v>
+        <v>-19.2408</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.606299999999999</v>
+        <v>-3.6062</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.3149</v>
+        <v>-15.6346</v>
       </c>
       <c r="G24" t="n">
         <v>-4.918399999999999</v>
@@ -2326,13 +2326,13 @@
         <v>11.9031</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.7615</v>
+        <v>-11.0815</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.5742</v>
+        <v>-6.5744</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.1874</v>
+        <v>-4.5072</v>
       </c>
       <c r="V24" t="n">
         <v>0.7264999999999997</v>
